--- a/output_docs/Master_Hospital_Billing.xlsx
+++ b/output_docs/Master_Hospital_Billing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,6 +952,4057 @@
         <v>150</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BED CHARGES</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PATHOLOGY INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DOCTOR FEES</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PROCEDURES</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OTHER CHARGES</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DRUGS AND CONSUMABLES</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>90540.95</v>
+      </c>
+      <c r="F28" t="n">
+        <v>90540.95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PHARMACY BILL</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14170.71</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14170.71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PHARMACY SALES RETURN</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-3585.94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-3585.94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pharmacy Bill</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12336.72</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12336.72</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12336.72</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12336.72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BED CHARGES BEDCHARGE: PRIVATE NON AC/Z B/711</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BED CHARGES BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMIPrivate Non Ac</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PATHOLOGY INVESTIGATION :- BLOOD GASES</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>300</v>
+      </c>
+      <c r="F36" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HAEMOGRAMIPANEL]</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RFTIPANELI</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>700</v>
+      </c>
+      <c r="F38" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DOCTOR FEES :- ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>600</v>
+      </c>
+      <c r="F39" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PROCEDURES:. BSL ON GLUCOMETER</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>130</v>
+      </c>
+      <c r="F40" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ECG CHARGES ER1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>300</v>
+      </c>
+      <c r="F41" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ER CHARGES rPD</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>200</v>
+      </c>
+      <c r="F43" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INTRACATH INSERTION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>90540.95</v>
+      </c>
+      <c r="F47" t="n">
+        <v>90540.95</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bill :11842627/52655</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bill:11842627152785</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bill :12072627155926</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bill :10752627/59582</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bill:11842627153272</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bill :11842627153306</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bill :11842627/53513</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BED CHARGES</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PHARMACY BILL</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bill:11842627153881</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>400</v>
+      </c>
+      <c r="F58" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bill:11842627154031</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bill:11842627154078</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="F60" t="n">
+        <v>44.92</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bill:11842627154172</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bill:11842627154587</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="F62" t="n">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bill :11842627/54609</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Department : Bill:1082262717990</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1992.97</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1992.97</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="F65" t="n">
+        <v>84.41</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EXTENSION TUBE lOCM WTH 5LO8S</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>280</v>
+      </c>
+      <c r="F66" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VENFLON SAFETY 2OG-393244</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>460.01</v>
+      </c>
+      <c r="F67" t="n">
+        <v>460.01</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ICO ASPIRATOR SYR 1.sIuL zKo1 o2t022028</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>45</v>
+      </c>
+      <c r="F68" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GLOVES EXAM. MEXISAFEM 003</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>14</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NS FLEXIDRIP IV 1OOML OTSUKA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="F70" t="n">
+        <v>44.92</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HOSPIMOL UB IV lOOOMG/1OOML</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PANTOCIDIV4OMG NPC00048</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="F72" t="n">
+        <v>53.89</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5CCSYR OMNIVAN24X 1 25L13M4202</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>11</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>I V SET ROfuISON TRANSFLOW. K268010680</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>80</v>
+      </c>
+      <c r="F74" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VELFIX-EDGE 7X9CM</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>213</v>
+      </c>
+      <c r="F75" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0-SYTE BD-385103</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>412</v>
+      </c>
+      <c r="F76" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F77" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PROBE COVER FOR THERMOSCAN</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F78" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PAUSE INJ SOOI/lG/sML EM260'192</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="F79" t="n">
+        <v>147.38</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ONDEM INJ 4I'G/2ML SGOND26O79</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F80" t="n">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE lOML</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE lOML</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>7</v>
+      </c>
+      <c r="E84" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>388.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="F85" t="n">
+        <v>92.51000000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>REVELOL AM 50/5TAB JKN0'125006AS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F86" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F87" t="n">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>THALIX CAPS sOMG THA25O914</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>133.12</v>
+      </c>
+      <c r="F88" t="n">
+        <v>133.12</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OCTRIDE INJ 100MCG/ML GTH0115A O1|12DO2A</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4950</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IMLSYRTUBERCUIlN 6064263</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>72</v>
+      </c>
+      <c r="E90" t="n">
+        <v>123984</v>
+      </c>
+      <c r="F90" t="n">
+        <v>123984</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IRNY INJ 1000MG/20M1 G250545</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3608.2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3608.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>STERIPORT TOTAL NS IV 60650233</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="F92" t="n">
+        <v>66.77</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>STERIPORTTOTAL NS IV 60660233</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="F93" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>lML SYR TUBERCULIN 6064263</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>600</v>
+      </c>
+      <c r="F94" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>THALIX CAPS SOMG TH4250914</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>166.39</v>
+      </c>
+      <c r="F95" t="n">
+        <v>166.39</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TEGADERM 1633 lN7X8.5 R03260914</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>220</v>
+      </c>
+      <c r="F96" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VASOFIX SAFETY 22G 25M10G8A0'1</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>180</v>
+      </c>
+      <c r="F97" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>IMLSYRTUBERCUL|N 6064263 2A021203'1</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>96</v>
+      </c>
+      <c r="F98" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>5</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OCTRIDE INJ 100MCG/1ML GTH0115A</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NS FLEXTDRTP lV I00MLOTSUKq 1256913</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="F100" t="n">
+        <v>44.52</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OCTRIDEINJ'|ooMCG/|ML GTH0115A S'll12Do28</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE 10ML 80003264</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="n">
+        <v>88</v>
+      </c>
+      <c r="F102" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MBLET TAB 2OMG U802884</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>358.75</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>5</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TMLSYRTUBERCULTN 6064263 28t021203,1</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>216</v>
+      </c>
+      <c r="F104" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>5</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OCTRIDEINJ Io0MCG/1ML GTH0115A</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4950</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>REVELOLAM 5O/5TAB JKN014008AS</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="F106" t="n">
+        <v>64.48</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>8</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Inj Octreotide lOOmcg 1-0-l for 15 days then stop</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>500</v>
+      </c>
+      <c r="F107" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BED CHARGES</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PATHOLOGY INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DOCTOR FEES</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PROCEDURES</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>OTHER CHARGES</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DRUGS AND CONSUMABLES</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PHARMACY BILL</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PHARMACY SALES RETURN</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BEDCHARGE: PRIVATE NON AC/Z B/711</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F116" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMI PRIVATE NON AC</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BLOOD GASES</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>300</v>
+      </c>
+      <c r="F118" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HAEMOGRAMIPANEL]</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RFTIPANELI</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>700</v>
+      </c>
+      <c r="F120" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>600</v>
+      </c>
+      <c r="F121" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BSL ON GLUCOMETER</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>130</v>
+      </c>
+      <c r="F122" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ECG CHARGES ER1</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>300</v>
+      </c>
+      <c r="F123" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ER CHARGES rPD</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>I.V.INFUSION</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>200</v>
+      </c>
+      <c r="F125" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>INTRACATH INSERTION</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>50</v>
+      </c>
+      <c r="F127" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>150</v>
+      </c>
+      <c r="F128" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>90540.95</v>
+      </c>
+      <c r="F129" t="n">
+        <v>90540.95</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Bill :11842627/52655</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1535.73</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1535.73</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Bill:11842627152785</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F131" t="n">
+        <v>66.56</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Bill :12072627155926</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="F132" t="n">
+        <v>32.24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bill :10752627/59582</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="F133" t="n">
+        <v>84.41</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Bill:11842627153272</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Bill :11842627153306</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3608.2</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3608.2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="F136" t="n">
+        <v>66.77</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Bill :11842627/53513</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>286.39</v>
+      </c>
+      <c r="F137" t="n">
+        <v>286.39</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bill:11842627153881</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>400</v>
+      </c>
+      <c r="F138" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Bill:11842627154031</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1148</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Bill:11842627154078</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="F140" t="n">
+        <v>44.92</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Bill:11842627154172</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bill:11842627154587</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="F142" t="n">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Bill :11842627/54609</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Bill:1082262717990</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1992.97</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1992.97</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PHARMACY SALES RETURN</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-3585.94</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-3585.94</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AL-01-4433 REVELOL AM 5O/5TAB</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Single ltem Pharmacy Retail</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="F147" t="n">
+        <v>84.41</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SR.O2-01'16 EXTENSION TUBE lOCM WTH 5LO8S 3WAY</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>280</v>
+      </c>
+      <c r="F148" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SR-02-2020 VENFLON SAFETY 2OG-393244</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>460.01</v>
+      </c>
+      <c r="F149" t="n">
+        <v>460.01</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>4</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SR-03-0,149 S 95 A 6 F - E 62 P 2 ICO ASPIRATOR SYR 1.sIuL</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>45</v>
+      </c>
+      <c r="F150" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sR-06-2151 GLOVES EXAM. MEXISAFEM</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>14</v>
+      </c>
+      <c r="F151" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>A1.03.0463 NS FLEXIDRIP IV 1OOML OTSUKA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="F152" t="n">
+        <v>44.92</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>41.03.0415 HOSPIMOL UB IV lOOOMG/1OOML</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>110</v>
+      </c>
+      <c r="F153" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>4</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AL.O3.OO54 PANTOCIDIV4OMG</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="F154" t="n">
+        <v>53.89</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sR-03-0075 5CCSYR OMNIVAN24X</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>11</v>
+      </c>
+      <c r="F155" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SR.03.0148 I V SET ROfuISON TRANSFLOW.</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>80</v>
+      </c>
+      <c r="F156" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>4</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SR-01-0673 VELFIX-EDGE 7X9CM</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>213</v>
+      </c>
+      <c r="F157" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sR-06-2953 0-SYTE BD-385103</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>412</v>
+      </c>
+      <c r="F158" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>REVELOL AM 5O/5TAB</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>4</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PROBE COVER FOR THERMOSCAN</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F161" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>4</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>PROBE COVER FOR THERMOSCAN</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F162" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>4</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PAUSE INJ SOOI/lG/sML</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="F163" t="n">
+        <v>147.38</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ONDEM INJ 4I'G/2ML</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="F164" t="n">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F166" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE lOML</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F167" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE lOML</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>7</v>
+      </c>
+      <c r="E168" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="F168" t="n">
+        <v>388.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>4</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>lOCC SYR OIVNIVAN 21 X 1.5</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>5</v>
+      </c>
+      <c r="E169" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="F169" t="n">
+        <v>92.51000000000001</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>5CC SYR OMNIVAN 24 X 1</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" t="n">
+        <v>11</v>
+      </c>
+      <c r="F170" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>4</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ECOFLAC PLUS NS O.9GM/'IOOML</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" t="n">
+        <v>180</v>
+      </c>
+      <c r="F171" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>4</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ALCOHOL SWAB ROMSON</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>7</v>
+      </c>
+      <c r="E172" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="F172" t="n">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>4</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>REVELOL AM 5O/5TAB</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>5</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>3</v>
+      </c>
+      <c r="E174" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>THALIX CAPS sOMG</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F175" t="n">
+        <v>66.56</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>4</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>OCTRIDE INJ 100MCG/|ML</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>IMLSYRTUBERCUIlN</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>72</v>
+      </c>
+      <c r="F177" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>4</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>IRNY INJ 1000MG/20M1</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3608.2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>3608.2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>STERIPORTTOTAL NS IV 2 25GM/25OML AMANTA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="F179" t="n">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>lML SYR TUBERCULIN</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>5</v>
+      </c>
+      <c r="E180" t="n">
+        <v>24</v>
+      </c>
+      <c r="F180" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>THALIX CAPS SOMG</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" t="n">
+        <v>166.39</v>
+      </c>
+      <c r="F181" t="n">
+        <v>166.39</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TEGADERM 1633 lN7X8.5</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>220</v>
+      </c>
+      <c r="F182" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>VASOFIX SAFETY 22G</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>180</v>
+      </c>
+      <c r="F183" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>IMLSYRTUBERCUL|N</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>48</v>
+      </c>
+      <c r="F184" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>OCTRIDE INJ 100MCG/1ML</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>OCTRIDEINJ'|ooMCG/|ML</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>550</v>
+      </c>
+      <c r="F186" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE 10ML</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" t="n">
+        <v>222</v>
+      </c>
+      <c r="F187" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MBLET TAB 2OMG</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="F188" t="n">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>'TMLSYRTUBERCULTN</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>3</v>
+      </c>
+      <c r="E189" t="n">
+        <v>72</v>
+      </c>
+      <c r="F189" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>5</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>OCTRIDEINJ Io0MCG/1ML</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>3</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4950</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>doc3.pdf</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>5</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>REVELOLAM 5O/5TAB</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="F191" t="n">
+        <v>32.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_docs/Master_Hospital_Billing.xlsx
+++ b/output_docs/Master_Hospital_Billing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -459,23 +459,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Admission Charges</t>
+          <t>ADMINISTRATIVE CHARGES</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2140</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>2140</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,23 +483,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consultation OP</t>
+          <t>ADMISSION</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1050</v>
+        <v>220</v>
       </c>
       <c r="F3" t="n">
-        <v>1050</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -507,23 +507,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>BED CHARGES</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>5100</v>
+        <v>1540</v>
       </c>
       <c r="F4" t="n">
-        <v>5100</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -531,23 +531,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Procedures</t>
+          <t>DIETETICS DEPARTMENT</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>4560</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>4560</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -555,23 +555,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PPNCO3-ANGIOGRAPHY WITH ANGIOPLASTY</t>
+          <t>DOCTORS VISIT CHARGE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>183969</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>183969</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -579,23 +579,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pharmacy Drugs Materials</t>
+          <t>LABORATORY</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>20624.97</v>
+        <v>1001</v>
       </c>
       <c r="F7" t="n">
-        <v>20624.97</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -603,23 +603,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CATHETERS TIGER 5 F 100CM RADIAL # RH*STIGIIOM- TERUMO</t>
+          <t>Dengue Ns1ag-Igg-Igm Card Test</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2709</v>
+        <v>660</v>
       </c>
       <c r="F8" t="n">
-        <v>2709</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -627,23 +627,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONARY GUIDING CATHETER POWER BACK UP 6F 1O0CM HYPERION HWgOpb35OP10000 ASAHI</t>
+          <t>Combo</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6984</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>6984</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -651,23 +651,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EMERALD GUIDE WIRE ANGIO  035 X 150 CM J TIP 502521, CORDIS</t>
+          <t>Leptospira - Igg</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1285</v>
+        <v>1485</v>
       </c>
       <c r="F10" t="n">
-        <v>1285</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -675,23 +675,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUIDE WIRE PTCA SION BLUE ES J-TIP 0.14 INCH X 190 CM, #AHWIARO17J,ASAHI INTEC</t>
+          <t>Leptospira - Igm</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>8438</v>
+        <v>550</v>
       </c>
       <c r="F11" t="n">
-        <v>8438</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -699,23 +699,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TRAVELLER NC BALLOON PTCA 4.0MM X 12MM 143CM 1013157 12, ABBOTT</t>
+          <t>Lft</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>18750</v>
+        <v>418</v>
       </c>
       <c r="F12" t="n">
-        <v>18750</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -723,23 +723,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>STENT BIOMATRIX ALPHA 4.0 MM X 19 MM #BMX6-4019, BIOSENSORS</t>
+          <t>Renal Function TestUrea Creat Uric Acid</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>41145.33</v>
+        <v>308</v>
       </c>
       <c r="F13" t="n">
-        <v>41145.33</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -747,23 +747,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[DIET037] Veg Cheese 5 'wich</t>
+          <t>Scrub Typhus Elisa</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -771,167 +771,167 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[DIET1083] Chapati 1  pcs</t>
+          <t>Serum Electrolytes</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[DIET1291] DAL TADKEWALI</t>
+          <t>Tsh</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[DIET2074] Choice Of Bhindi Masala Kurkuri</t>
+          <t>Crp</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>385</v>
       </c>
       <c r="F17" t="n">
-        <v>150</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[DIET2078] Egg Thali</t>
+          <t>Grbs</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[DIET3OO] Mineral Water 1 Lt.</t>
+          <t>Platelet Count</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[CGSTBED] CGST on Bed Charge 2 .5%</t>
+          <t>Sodium, Potassium</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>337</v>
+        <v>264</v>
       </c>
       <c r="F20" t="n">
-        <v>337</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[SGSTBED] SGST on Bed Charge 2 .5%</t>
+          <t>Total Wbc Count Tc</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>337</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>337</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>doc2.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -939,287 +939,278 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MANIPAL HOSPITAL BANER-PUNE</t>
+          <t>Std Ac Room-2-Dw8</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="F22" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BED CHARGES</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11000</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11000</v>
+          <t>PROCEDURE/SERVICE CHARGE</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PATHOLOGY INVESTIGATION</t>
+          <t>Ecg</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>2260</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>2260</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DOCTOR FEES</t>
+          <t>8x10 Film</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>6800</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>6800</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PROCEDURES</t>
+          <t>Xray Chest - Pa View</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1980</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
-        <v>1980</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>10 Ml Syringe</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>31.5</v>
       </c>
       <c r="F27" t="n">
-        <v>200</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DRUGS AND CONSUMABLES</t>
+          <t>2 Ml Syringe Dis</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>90540.95</v>
+        <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>90540.95</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PHARMACY BILL</t>
+          <t>2 Ml Syringe Dis</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>14170.71</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>14170.71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PHARMACY SALES RETURN</t>
+          <t>5 Ml Syringe Dis</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>-3585.94</v>
+        <v>16.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-3585.94</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pharmacy Bill</t>
+          <t>Drip Set Dis Drip Set Dis</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1000</v>
+        <v>201</v>
       </c>
       <c r="F31" t="n">
-        <v>1000</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGST</t>
+          <t>Needle 16*1 1/2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>12336.72</v>
+        <v>5.32</v>
       </c>
       <c r="F32" t="n">
-        <v>12336.72</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SGST</t>
+          <t>Needle 16*1 1/2</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>12336.72</v>
+        <v>5.32</v>
       </c>
       <c r="F33" t="n">
-        <v>12336.72</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1227,23 +1218,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BED CHARGES BEDCHARGE: PRIVATE NON AC/Z B/711</t>
+          <t>Needle 24* 1/2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>7000</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>7000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1251,23 +1242,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BED CHARGES BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMIPrivate Non Ac</t>
+          <t>Needle 26*1/2</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1275,23 +1266,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PATHOLOGY INVESTIGATION :- BLOOD GASES</t>
+          <t>Vitcee Fort</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>300</v>
+        <v>445.32</v>
       </c>
       <c r="F36" t="n">
-        <v>300</v>
+        <v>445.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1299,23 +1290,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HAEMOGRAMIPANEL]</t>
+          <t>10 Ml Syringe</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>1260</v>
+        <v>31.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1260</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1323,23 +1314,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RFTIPANELI</t>
+          <t>Drip Set Dis</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>700</v>
+        <v>201</v>
       </c>
       <c r="F38" t="n">
-        <v>700</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1347,23 +1338,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DOCTOR FEES :- ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
+          <t>Easy Fix</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>600</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>600</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1371,23 +1362,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PROCEDURES:. BSL ON GLUCOMETER</t>
+          <t>Iv Cannula 24g Dis</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>130</v>
+        <v>191.25</v>
       </c>
       <c r="F40" t="n">
-        <v>130</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1395,23 +1386,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ECG CHARGES ER1</t>
+          <t>Abiflu 75 Cap</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>300</v>
+        <v>46.73</v>
       </c>
       <c r="F41" t="n">
-        <v>300</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1419,23 +1410,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ER CHARGES rPD</t>
+          <t>Bidel 100mg Inj Bidel 100mg Inj</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1250</v>
+        <v>536.91</v>
       </c>
       <c r="F42" t="n">
-        <v>1250</v>
+        <v>536.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1443,359 +1434,359 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>I.V.INFUSION</t>
+          <t>Espentral - 40</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="F43" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INTRACATH INSERTION</t>
+          <t>Fexolite M Tab</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1980</v>
+        <v>98</v>
       </c>
       <c r="F44" t="n">
-        <v>1980</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
+          <t>Livi 300mg Tab</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
+          <t>Menis - Sb Inj</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>200000</v>
+        <v>3093.75</v>
       </c>
       <c r="F46" t="n">
-        <v>200000</v>
+        <v>3093.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
+          <t>Meronorm 1gm Inj</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>90540.95</v>
+        <v>1331.24</v>
       </c>
       <c r="F47" t="n">
-        <v>90540.95</v>
+        <v>1331.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bill :11842627/52655</t>
+          <t>Normal Saline 100ml</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>90.44</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bill:11842627152785</t>
+          <t>Normal Saline 100ml</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bill :12072627155926</t>
+          <t>Normal Saline Ivf</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>94.55</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bill :10752627/59582</t>
+          <t>Piximole 100 Ml</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bill:11842627153272</t>
+          <t>Polybion Inj</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>25.78</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bill :11842627153306</t>
+          <t>Ringer Lactate Ivf</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>138.78</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>138.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
+          <t>Bidel 100mg Inj</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1073.82</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1073.82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bill :11842627/53513</t>
+          <t>Espentral - 40</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BED CHARGES</t>
+          <t>Menis - Sb Inj</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>1000</v>
+        <v>3093.74</v>
       </c>
       <c r="F56" t="n">
-        <v>1000</v>
+        <v>3093.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PHARMACY BILL</t>
+          <t>Normal Saline 100ml</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>1000</v>
+        <v>135</v>
       </c>
       <c r="F57" t="n">
-        <v>1000</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1803,23 +1794,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bill:11842627153881</t>
+          <t>Abiflu 75 Cap</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>400</v>
+        <v>280.4</v>
       </c>
       <c r="F58" t="n">
-        <v>400</v>
+        <v>280.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1827,23 +1818,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bill:11842627154031</t>
+          <t>Doxy 1 Tab</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>1148</v>
+        <v>158.48</v>
       </c>
       <c r="F59" t="n">
-        <v>1148</v>
+        <v>158.48</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1851,23 +1842,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bill:11842627154078</t>
+          <t>Emeset Inj 2 Ml</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>44.92</v>
+        <v>25.44</v>
       </c>
       <c r="F60" t="n">
-        <v>44.92</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1875,23 +1866,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bill:11842627154172</t>
+          <t>Farotic 200</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E61" t="n">
-        <v>1322</v>
+        <v>2362.5</v>
       </c>
       <c r="F61" t="n">
-        <v>1322</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1899,23 +1890,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bill:11842627154587</t>
+          <t>Fexolite M Tab</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>71.75</v>
+        <v>16.34</v>
       </c>
       <c r="F62" t="n">
-        <v>71.75</v>
+        <v>98.04000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1923,23 +1914,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bill :11842627/54609</t>
+          <t>Fexolite M Tab</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>1722</v>
+        <v>16.34</v>
       </c>
       <c r="F63" t="n">
-        <v>1722</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1947,857 +1938,857 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Department : Bill:1082262717990</t>
+          <t>Piximole 100 Ml</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>1992.97</v>
+        <v>299</v>
       </c>
       <c r="F64" t="n">
-        <v>1992.97</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
+          <t>Probotix Cap</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
-        <v>84.41</v>
+        <v>16.91</v>
       </c>
       <c r="F65" t="n">
-        <v>84.41</v>
+        <v>236.74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EXTENSION TUBE lOCM WTH 5LO8S</t>
+          <t>Supralite Os Syp</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="F66" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VENFLON SAFETY 2OG-393244</t>
+          <t>Triavit Plus Cap</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>460.01</v>
+        <v>17.34</v>
       </c>
       <c r="F67" t="n">
-        <v>460.01</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ICO ASPIRATOR SYR 1.sIuL zKo1 o2t022028</t>
+          <t>Voqozon</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>45</v>
+        <v>19.69</v>
       </c>
       <c r="F68" t="n">
-        <v>45</v>
+        <v>275.66</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GLOVES EXAM. MEXISAFEM 003</t>
+          <t>Administrative Charges</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F69" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NS FLEXIDRIP IV 1OOML OTSUKA</t>
+          <t>Admission</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>44.92</v>
+        <v>220</v>
       </c>
       <c r="F70" t="n">
-        <v>44.92</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HOSPIMOL UB IV lOOOMG/1OOML</t>
+          <t>Bed Charges</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>4620</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PANTOCIDIV4OMG NPC00048</t>
+          <t>Dietetics Department</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>53.89</v>
+        <v>110</v>
       </c>
       <c r="F72" t="n">
-        <v>53.89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5CCSYR OMNIVAN24X 1 25L13M4202</t>
+          <t>Doctors Visit Charge</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>330</v>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>I V SET ROfuISON TRANSFLOW. K268010680</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>80</v>
+        <v>7733</v>
       </c>
       <c r="F74" t="n">
-        <v>80</v>
+        <v>7733</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VELFIX-EDGE 7X9CM</t>
+          <t>Medicine Charges</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>213</v>
+        <v>20217.4</v>
       </c>
       <c r="F75" t="n">
-        <v>213</v>
+        <v>20217.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0-SYTE BD-385103</t>
+          <t>Nursing Charges</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>412</v>
+        <v>660</v>
       </c>
       <c r="F76" t="n">
-        <v>412</v>
+        <v>660</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
+          <t>Procedure/Service Charge</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>9.52</v>
+        <v>220</v>
       </c>
       <c r="F77" t="n">
-        <v>9.52</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PROBE COVER FOR THERMOSCAN</t>
+          <t>Radiology</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>9.52</v>
+        <v>341</v>
       </c>
       <c r="F78" t="n">
-        <v>9.52</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PAUSE INJ SOOI/lG/sML EM260'192</t>
+          <t>Admission Charges</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>147.38</v>
+        <v>2140</v>
       </c>
       <c r="F79" t="n">
-        <v>147.38</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ONDEM INJ 4I'G/2ML SGOND26O79</t>
+          <t>Consultation OP</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>12.73</v>
+        <v>1050</v>
       </c>
       <c r="F80" t="n">
-        <v>12.73</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>18.5</v>
+        <v>5100</v>
       </c>
       <c r="F81" t="n">
-        <v>18.5</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2CC SYR OMNIVAN 24 X 1</t>
+          <t>Procedures</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>9.5</v>
+        <v>4560</v>
       </c>
       <c r="F82" t="n">
-        <v>9.5</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE lOML</t>
+          <t>PPNCO3-ANGIOGRAPHY WITH ANGIOPLASTY</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>55.5</v>
+        <v>183969</v>
       </c>
       <c r="F83" t="n">
-        <v>55.5</v>
+        <v>183969</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE lOML</t>
+          <t>Pharmacy Drugs Materials</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>388.5</v>
+        <v>20624.97</v>
       </c>
       <c r="F84" t="n">
-        <v>388.5</v>
+        <v>20624.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+          <t>CATHETERS TIGER 5 F 100CM RADIAL # RH*STIGIIOM- TERUMO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>92.51000000000001</v>
+        <v>2709</v>
       </c>
       <c r="F85" t="n">
-        <v>92.51000000000001</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REVELOL AM 50/5TAB JKN0'125006AS</t>
+          <t>CORONARY GUIDING CATHETER POWER BACK UP 6F 1O0CM HYPERION HWgOpb35OP10000 ASAHI</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>28.5</v>
+        <v>6984</v>
       </c>
       <c r="F86" t="n">
-        <v>28.5</v>
+        <v>6984</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2CC SYR OMNIVAN 24 X 1</t>
+          <t>EMERALD GUIDE WIRE ANGIO  035 X 150 CM J TIP 502521, CORDIS</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>85.5</v>
+        <v>1285</v>
       </c>
       <c r="F87" t="n">
-        <v>85.5</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>THALIX CAPS sOMG THA25O914</t>
+          <t>GUIDE WIRE PTCA SION BLUE ES J-TIP 0.14 INCH X 190 CM, #AHWIARO17J,ASAHI INTEC</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>133.12</v>
+        <v>8438</v>
       </c>
       <c r="F88" t="n">
-        <v>133.12</v>
+        <v>8438</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OCTRIDE INJ 100MCG/ML GTH0115A O1|12DO2A</t>
+          <t>TRAVELLER NC BALLOON PTCA 4.0MM X 12MM 143CM 1013157 12, ABBOTT</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>4950</v>
+        <v>18750</v>
       </c>
       <c r="F89" t="n">
-        <v>4950</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IMLSYRTUBERCUIlN 6064263</t>
+          <t>STENT BIOMATRIX ALPHA 4.0 MM X 19 MM #BMX6-4019, BIOSENSORS</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>123984</v>
+        <v>41145.33</v>
       </c>
       <c r="F90" t="n">
-        <v>123984</v>
+        <v>41145.33</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IRNY INJ 1000MG/20M1 G250545</t>
+          <t>[DIET037] Veg Cheese 5 'wich</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>3608.2</v>
+        <v>120</v>
       </c>
       <c r="F91" t="n">
-        <v>3608.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STERIPORT TOTAL NS IV 60650233</t>
+          <t>[DIET1083] Chapati 1  pcs</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
-        <v>66.77</v>
+        <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>66.77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STERIPORTTOTAL NS IV 60660233</t>
+          <t>[DIET1291] DAL TADKEWALI</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>6.77</v>
+        <v>150</v>
       </c>
       <c r="F93" t="n">
-        <v>6.77</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>lML SYR TUBERCULIN 6064263</t>
+          <t>[DIET2074] Choice Of Bhindi Masala Kurkuri</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="F94" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>THALIX CAPS SOMG TH4250914</t>
+          <t>[DIET2078] Egg Thali</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>166.39</v>
+        <v>190</v>
       </c>
       <c r="F95" t="n">
-        <v>166.39</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TEGADERM 1633 lN7X8.5 R03260914</t>
+          <t>[DIET3OO] Mineral Water 1 Lt.</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="F96" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VASOFIX SAFETY 22G 25M10G8A0'1</t>
+          <t>[CGSTBED] CGST on Bed Charge 2 .5%</t>
         </is>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="F97" t="n">
-        <v>180</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IMLSYRTUBERCUL|N 6064263 2A021203'1</t>
+          <t>[SGSTBED] SGST on Bed Charge 2 .5%</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="F98" t="n">
-        <v>96</v>
+        <v>337</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>doc3.pdf</t>
+          <t>doc2.pdf</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OCTRIDE INJ 100MCG/1ML GTH0115A</t>
+          <t>MANIPAL HOSPITAL BANER-PUNE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="F99" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100">
@@ -2807,21 +2798,21 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NS FLEXTDRTP lV I00MLOTSUKq 1256913</t>
+          <t>BED CHARGES</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>44.52</v>
+        <v>11000</v>
       </c>
       <c r="F100" t="n">
-        <v>44.52</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="101">
@@ -2831,21 +2822,21 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OCTRIDEINJ'|ooMCG/|ML GTH0115A S'll12Do28</t>
+          <t>PATHOLOGY INVESTIGATION</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1100</v>
+        <v>2260</v>
       </c>
       <c r="F101" t="n">
-        <v>1100</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="102">
@@ -2855,21 +2846,21 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE 10ML 80003264</t>
+          <t>DOCTOR FEES</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>88</v>
+        <v>6800</v>
       </c>
       <c r="F102" t="n">
-        <v>88</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="103">
@@ -2879,21 +2870,21 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MBLET TAB 2OMG U802884</t>
+          <t>PROCEDURES</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>358.75</v>
+        <v>1980</v>
       </c>
       <c r="F103" t="n">
-        <v>358.75</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="104">
@@ -2903,21 +2894,21 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TMLSYRTUBERCULTN 6064263 28t021203,1</t>
+          <t>OTHER CHARGES</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="F104" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105">
@@ -2927,21 +2918,21 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OCTRIDEINJ Io0MCG/1ML GTH0115A</t>
+          <t>DRUGS AND CONSUMABLES</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>4950</v>
+        <v>90540.95</v>
       </c>
       <c r="F105" t="n">
-        <v>4950</v>
+        <v>90540.95</v>
       </c>
     </row>
     <row r="106">
@@ -2951,21 +2942,21 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>REVELOLAM 5O/5TAB JKN014008AS</t>
+          <t>PHARMACY BILL</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>64.48</v>
+        <v>14170.71</v>
       </c>
       <c r="F106" t="n">
-        <v>64.48</v>
+        <v>14170.71</v>
       </c>
     </row>
     <row r="107">
@@ -2975,21 +2966,21 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Inj Octreotide lOOmcg 1-0-l for 15 days then stop</t>
+          <t>PHARMACY SALES RETURN</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>500</v>
+        <v>-3585.94</v>
       </c>
       <c r="F107" t="n">
-        <v>500</v>
+        <v>-3585.94</v>
       </c>
     </row>
     <row r="108">
@@ -3003,17 +2994,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BED CHARGES</t>
+          <t>Pharmacy Bill</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="109">
@@ -3027,17 +3018,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PATHOLOGY INVESTIGATION</t>
+          <t>CGST</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>12336.72</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>12336.72</v>
       </c>
     </row>
     <row r="110">
@@ -3051,17 +3042,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DOCTOR FEES</t>
+          <t>SGST</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>12336.72</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>12336.72</v>
       </c>
     </row>
     <row r="111">
@@ -3071,21 +3062,21 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PROCEDURES</t>
+          <t>BED CHARGES BEDCHARGE: PRIVATE NON AC/Z B/711</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="112">
@@ -3095,21 +3086,21 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OTHER CHARGES</t>
+          <t>BED CHARGES BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMIPrivate Non Ac</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="113">
@@ -3119,21 +3110,21 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DRUGS AND CONSUMABLES</t>
+          <t>PATHOLOGY INVESTIGATION :- BLOOD GASES</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114">
@@ -3143,21 +3134,21 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PHARMACY BILL</t>
+          <t>HAEMOGRAMIPANEL]</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="115">
@@ -3167,21 +3158,21 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PHARMACY SALES RETURN</t>
+          <t>RFTIPANELI</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="116">
@@ -3195,17 +3186,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BEDCHARGE: PRIVATE NON AC/Z B/711</t>
+          <t>DOCTOR FEES :- ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>7000</v>
+        <v>600</v>
       </c>
       <c r="F116" t="n">
-        <v>7000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="117">
@@ -3219,17 +3210,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMI PRIVATE NON AC</t>
+          <t>PROCEDURES:. BSL ON GLUCOMETER</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>2000</v>
+        <v>130</v>
       </c>
       <c r="F117" t="n">
-        <v>2000</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118">
@@ -3243,7 +3234,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BLOOD GASES</t>
+          <t>ECG CHARGES ER1</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3267,17 +3258,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HAEMOGRAMIPANEL]</t>
+          <t>ER CHARGES rPD</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="F119" t="n">
-        <v>1260</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="120">
@@ -3291,17 +3282,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RFTIPANELI</t>
+          <t>I.V.INFUSION</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F120" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121">
@@ -3315,17 +3306,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
+          <t>INTRACATH INSERTION</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>600</v>
+        <v>1980</v>
       </c>
       <c r="F121" t="n">
-        <v>600</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="122">
@@ -3339,17 +3330,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BSL ON GLUCOMETER</t>
+          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
         </is>
       </c>
       <c r="D122" t="n">
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3363,17 +3354,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ECG CHARGES ER1</t>
+          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
         </is>
       </c>
       <c r="D123" t="n">
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>300</v>
+        <v>200000</v>
       </c>
       <c r="F123" t="n">
-        <v>300</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="124">
@@ -3387,17 +3378,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ER CHARGES rPD</t>
+          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
         </is>
       </c>
       <c r="D124" t="n">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>1250</v>
+        <v>90540.95</v>
       </c>
       <c r="F124" t="n">
-        <v>1250</v>
+        <v>90540.95</v>
       </c>
     </row>
     <row r="125">
@@ -3411,17 +3402,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>I.V.INFUSION</t>
+          <t>Bill :11842627/52655</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3435,17 +3426,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>INTRACATH INSERTION</t>
+          <t>Bill:11842627152785</t>
         </is>
       </c>
       <c r="D126" t="n">
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3459,17 +3450,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
+          <t>Bill :12072627155926</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3483,17 +3474,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
+          <t>Bill :10752627/59582</t>
         </is>
       </c>
       <c r="D128" t="n">
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3507,17 +3498,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
+          <t>Bill:11842627153272</t>
         </is>
       </c>
       <c r="D129" t="n">
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>90540.95</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>90540.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3531,17 +3522,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bill :11842627/52655</t>
+          <t>Bill :11842627153306</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1535.73</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>1535.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3555,17 +3546,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bill:11842627152785</t>
+          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>66.56</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>66.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3579,17 +3570,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bill :12072627155926</t>
+          <t>Bill :11842627/53513</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>32.24</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>32.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3603,17 +3594,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bill :10752627/59582</t>
+          <t>BED CHARGES</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>84.41</v>
+        <v>1000</v>
       </c>
       <c r="F133" t="n">
-        <v>84.41</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="134">
@@ -3627,17 +3618,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bill:11842627153272</t>
+          <t>PHARMACY BILL</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>1722</v>
+        <v>1000</v>
       </c>
       <c r="F134" t="n">
-        <v>1722</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="135">
@@ -3647,21 +3638,21 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bill :11842627153306</t>
+          <t>Bill:11842627153881</t>
         </is>
       </c>
       <c r="D135" t="n">
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>3608.2</v>
+        <v>400</v>
       </c>
       <c r="F135" t="n">
-        <v>3608.2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136">
@@ -3671,21 +3662,21 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
+          <t>Bill:11842627154031</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>66.77</v>
+        <v>1148</v>
       </c>
       <c r="F136" t="n">
-        <v>66.77</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="137">
@@ -3695,21 +3686,21 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bill :11842627/53513</t>
+          <t>Bill:11842627154078</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>286.39</v>
+        <v>44.92</v>
       </c>
       <c r="F137" t="n">
-        <v>286.39</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="138">
@@ -3723,17 +3714,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bill:11842627153881</t>
+          <t>Bill:11842627154172</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>400</v>
+        <v>1322</v>
       </c>
       <c r="F138" t="n">
-        <v>400</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="139">
@@ -3747,17 +3738,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bill:11842627154031</t>
+          <t>Bill:11842627154587</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>1148</v>
+        <v>71.75</v>
       </c>
       <c r="F139" t="n">
-        <v>1148</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="140">
@@ -3771,17 +3762,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bill:11842627154078</t>
+          <t>Bill :11842627/54609</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>44.92</v>
+        <v>1722</v>
       </c>
       <c r="F140" t="n">
-        <v>44.92</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="141">
@@ -3795,17 +3786,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bill:11842627154172</t>
+          <t>PHARMACY BILL Department : Bill:1082262717990</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1322</v>
+        <v>1992.97</v>
       </c>
       <c r="F141" t="n">
-        <v>1322</v>
+        <v>1992.97</v>
       </c>
     </row>
     <row r="142">
@@ -3815,21 +3806,21 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bill:11842627154587</t>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>71.75</v>
+        <v>84.41</v>
       </c>
       <c r="F142" t="n">
-        <v>71.75</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="143">
@@ -3839,21 +3830,21 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bill :11842627/54609</t>
+          <t>EXTENSION TUBE lOCM WTH 5LO8S</t>
         </is>
       </c>
       <c r="D143" t="n">
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>1722</v>
+        <v>280</v>
       </c>
       <c r="F143" t="n">
-        <v>1722</v>
+        <v>280</v>
       </c>
     </row>
     <row r="144">
@@ -3863,21 +3854,21 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bill:1082262717990</t>
+          <t>VENFLON SAFETY 2OG-393244</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>1992.97</v>
+        <v>460.01</v>
       </c>
       <c r="F144" t="n">
-        <v>1992.97</v>
+        <v>460.01</v>
       </c>
     </row>
     <row r="145">
@@ -3887,21 +3878,21 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PHARMACY SALES RETURN</t>
+          <t>ASPIRATOR SYR 1.sIuL zKo1 o2t022028</t>
         </is>
       </c>
       <c r="D145" t="n">
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>-3585.94</v>
+        <v>45</v>
       </c>
       <c r="F145" t="n">
-        <v>-3585.94</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146">
@@ -3915,17 +3906,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AL-01-4433 REVELOL AM 5O/5TAB</t>
+          <t>GLOVES EXAM. MEXISAFEM 003</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>0.41</v>
+        <v>14</v>
       </c>
       <c r="F146" t="n">
-        <v>0.41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147">
@@ -3939,17 +3930,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Single ltem Pharmacy Retail</t>
+          <t>NS FLEXIDRIP IV 1OOML OTSUKA</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>84.41</v>
+        <v>44.92</v>
       </c>
       <c r="F147" t="n">
-        <v>84.41</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="148">
@@ -3963,17 +3954,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SR.O2-01'16 EXTENSION TUBE lOCM WTH 5LO8S 3WAY</t>
+          <t>HOSPIMOL UB IV lOOOMG/1OOML</t>
         </is>
       </c>
       <c r="D148" t="n">
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="F148" t="n">
-        <v>280</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
@@ -3987,17 +3978,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SR-02-2020 VENFLON SAFETY 2OG-393244</t>
+          <t>PANTOCIDIV4OMG NPC00048</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>460.01</v>
+        <v>53.89</v>
       </c>
       <c r="F149" t="n">
-        <v>460.01</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="150">
@@ -4011,17 +4002,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SR-03-0,149 S 95 A 6 F - E 62 P 2 ICO ASPIRATOR SYR 1.sIuL</t>
+          <t>5CCSYR OMNIVAN24X 1 25L13M4202</t>
         </is>
       </c>
       <c r="D150" t="n">
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F150" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
@@ -4035,17 +4026,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sR-06-2151 GLOVES EXAM. MEXISAFEM</t>
+          <t>I V SET ROfuISON TRANSFLOW.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="F151" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="152">
@@ -4059,17 +4050,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>A1.03.0463 NS FLEXIDRIP IV 1OOML OTSUKA</t>
+          <t>VELFIX-EDGE 7X9CM</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>44.92</v>
+        <v>213</v>
       </c>
       <c r="F152" t="n">
-        <v>44.92</v>
+        <v>213</v>
       </c>
     </row>
     <row r="153">
@@ -4083,17 +4074,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>41.03.0415 HOSPIMOL UB IV lOOOMG/1OOML</t>
+          <t>0-SYTE BD-385103</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>110</v>
+        <v>412</v>
       </c>
       <c r="F153" t="n">
-        <v>110</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154">
@@ -4107,17 +4098,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AL.O3.OO54 PANTOCIDIV4OMG</t>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS PROBE COVER FOR THERMOSCAN</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>53.89</v>
+        <v>9.52</v>
       </c>
       <c r="F154" t="n">
-        <v>53.89</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="155">
@@ -4131,17 +4122,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>sR-03-0075 5CCSYR OMNIVAN24X</t>
+          <t>PAUSE INJ SOOI/lG/sML EM260'192</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>11</v>
+        <v>294.76</v>
       </c>
       <c r="F155" t="n">
-        <v>11</v>
+        <v>294.76</v>
       </c>
     </row>
     <row r="156">
@@ -4155,17 +4146,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SR.03.0148 I V SET ROfuISON TRANSFLOW.</t>
+          <t>ONDEM INJ 4I'G/2ML SGOND26O79</t>
         </is>
       </c>
       <c r="D156" t="n">
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>80</v>
+        <v>12.73</v>
       </c>
       <c r="F156" t="n">
-        <v>80</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="157">
@@ -4179,17 +4170,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SR-01-0673 VELFIX-EDGE 7X9CM</t>
+          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
         </is>
       </c>
       <c r="D157" t="n">
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>213</v>
+        <v>18.5</v>
       </c>
       <c r="F157" t="n">
-        <v>213</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="158">
@@ -4203,17 +4194,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>sR-06-2953 0-SYTE BD-385103</t>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>412</v>
+        <v>9.5</v>
       </c>
       <c r="F158" t="n">
-        <v>412</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="159">
@@ -4227,17 +4218,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB</t>
+          <t>POLYFLUSH SYRINGE lOML</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E159" t="n">
-        <v>0.41</v>
+        <v>2719.5</v>
       </c>
       <c r="F159" t="n">
-        <v>0.41</v>
+        <v>2719.5</v>
       </c>
     </row>
     <row r="160">
@@ -4251,17 +4242,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PROBE COVER FOR THERMOSCAN</t>
+          <t>POLYFLUSH SYRINGE lOML</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>0.62</v>
+        <v>999</v>
       </c>
       <c r="F160" t="n">
-        <v>0.62</v>
+        <v>999</v>
       </c>
     </row>
     <row r="161">
@@ -4273,14 +4264,19 @@
       <c r="B161" t="n">
         <v>4</v>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>REVELOL AM 50/5TAB JKN0'125006AS</t>
+        </is>
+      </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>6.5</v>
+        <v>28.5</v>
       </c>
       <c r="F161" t="n">
-        <v>6.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="162">
@@ -4294,17 +4290,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PROBE COVER FOR THERMOSCAN</t>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E162" t="n">
-        <v>9.52</v>
+        <v>85.5</v>
       </c>
       <c r="F162" t="n">
-        <v>9.52</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="163">
@@ -4318,17 +4314,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PAUSE INJ SOOI/lG/sML</t>
+          <t>THALIX CAPS sOMG THA25O914</t>
         </is>
       </c>
       <c r="D163" t="n">
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>147.38</v>
+        <v>133.12</v>
       </c>
       <c r="F163" t="n">
-        <v>147.38</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="164">
@@ -4342,17 +4338,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ONDEM INJ 4I'G/2ML</t>
+          <t>OCTRIDE INJ 100MCG/ML GTH0115A O1|12DO2A</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>12.73</v>
+        <v>4950</v>
       </c>
       <c r="F164" t="n">
-        <v>12.73</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="165">
@@ -4366,17 +4362,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>lOCC SYR OMNIVAN 21 X 1.5</t>
+          <t>IMLSYRTUBERCUIlN 6064263</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E165" t="n">
-        <v>18.5</v>
+        <v>5184</v>
       </c>
       <c r="F165" t="n">
-        <v>18.5</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="166">
@@ -4390,17 +4386,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2CC SYR OMNIVAN 24 X 1</t>
+          <t>IRNY INJ 1000MG/20ML G250545</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>9.5</v>
+        <v>3608.2</v>
       </c>
       <c r="F166" t="n">
-        <v>9.5</v>
+        <v>3608.2</v>
       </c>
     </row>
     <row r="167">
@@ -4414,17 +4410,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE lOML</t>
+          <t>STERIPORT TOTAL NS IV 60650233</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>55.5</v>
+        <v>66.77</v>
       </c>
       <c r="F167" t="n">
-        <v>55.5</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="168">
@@ -4438,17 +4434,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE lOML</t>
+          <t>STERIPORTTOTAL NS IV 60660233</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>388.5</v>
+        <v>6.77</v>
       </c>
       <c r="F168" t="n">
-        <v>388.5</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="169">
@@ -4462,17 +4458,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>lOCC SYR OIVNIVAN 21 X 1.5</t>
+          <t>lML SYR TUBERCULIN 6064263</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>5</v>
       </c>
       <c r="E169" t="n">
-        <v>92.51000000000001</v>
+        <v>600</v>
       </c>
       <c r="F169" t="n">
-        <v>92.51000000000001</v>
+        <v>600</v>
       </c>
     </row>
     <row r="170">
@@ -4482,21 +4478,21 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>5CC SYR OMNIVAN 24 X 1</t>
+          <t>THALIX CAPS SOMG TH4250914</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>11</v>
+        <v>166.39</v>
       </c>
       <c r="F170" t="n">
-        <v>11</v>
+        <v>166.39</v>
       </c>
     </row>
     <row r="171">
@@ -4506,21 +4502,21 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ECOFLAC PLUS NS O.9GM/'IOOML</t>
+          <t>TEGADERM 1633 lN7X8.5 R03260914</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="F171" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="172">
@@ -4530,21 +4526,21 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ALCOHOL SWAB ROMSON</t>
+          <t>VASOFIX SAFETY 22G 25M10G8A0'1</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>19.25</v>
+        <v>180</v>
       </c>
       <c r="F172" t="n">
-        <v>19.25</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173">
@@ -4554,21 +4550,21 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB</t>
+          <t>IMLSYRTUBERCUL|N 6064263</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.41</v>
+        <v>96</v>
       </c>
       <c r="F173" t="n">
-        <v>0.41</v>
+        <v>96</v>
       </c>
     </row>
     <row r="174">
@@ -4578,21 +4574,21 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2CC SYR OMNIVAN 24 X 1</t>
+          <t>OCTRIDE INJ 100MCG/1ML GTH0115A</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>28.5</v>
+        <v>1100</v>
       </c>
       <c r="F174" t="n">
-        <v>28.5</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="175">
@@ -4602,21 +4598,21 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>THALIX CAPS sOMG</t>
+          <t>NS FLEXTDRTP lV I00MLOTSUKq</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>66.56</v>
+        <v>44.52</v>
       </c>
       <c r="F175" t="n">
-        <v>66.56</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="176">
@@ -4626,21 +4622,21 @@
         </is>
       </c>
       <c r="B176" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>OCTRIDEINJ'|ooMCG/|ML GTH0115A</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
         <v>4</v>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>OCTRIDE INJ 100MCG/|ML</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>3</v>
-      </c>
       <c r="E176" t="n">
-        <v>1650</v>
+        <v>2200</v>
       </c>
       <c r="F176" t="n">
-        <v>1650</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="177">
@@ -4650,21 +4646,21 @@
         </is>
       </c>
       <c r="B177" t="n">
+        <v>5</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>POLYFLUSH SYRINGE 10ML</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
         <v>4</v>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>IMLSYRTUBERCUIlN</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
       <c r="E177" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F177" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="178">
@@ -4674,21 +4670,21 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IRNY INJ 1000MG/20M1</t>
+          <t>MBLET TAB 2OMG U802884</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E178" t="n">
-        <v>3608.2</v>
+        <v>358.75</v>
       </c>
       <c r="F178" t="n">
-        <v>3608.2</v>
+        <v>358.75</v>
       </c>
     </row>
     <row r="179">
@@ -4698,21 +4694,21 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>STERIPORTTOTAL NS IV 2 25GM/25OML AMANTA</t>
+          <t>TMLSYRTUBERCULTN 6064263</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
-        <v>6.77</v>
+        <v>216</v>
       </c>
       <c r="F179" t="n">
-        <v>6.77</v>
+        <v>216</v>
       </c>
     </row>
     <row r="180">
@@ -4722,21 +4718,21 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>lML SYR TUBERCULIN</t>
+          <t>OCTRIDEINJ Io0MCG/1ML GTH0115A</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
-        <v>24</v>
+        <v>4950</v>
       </c>
       <c r="F180" t="n">
-        <v>24</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="181">
@@ -4750,17 +4746,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>THALIX CAPS SOMG</t>
+          <t>REVELOLAM 5O/5TAB JKN014008AS</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>166.39</v>
+        <v>64.48</v>
       </c>
       <c r="F181" t="n">
-        <v>166.39</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="182">
@@ -4770,237 +4766,21 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TEGADERM 1633 lN7X8.5</t>
+          <t>Inj Octreotide lOOmcg 1-0-l for 15 days then stop</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="F182" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>5</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>VASOFIX SAFETY 22G</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" t="n">
-        <v>180</v>
-      </c>
-      <c r="F183" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>5</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>IMLSYRTUBERCUL|N</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>2</v>
-      </c>
-      <c r="E184" t="n">
-        <v>48</v>
-      </c>
-      <c r="F184" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>5</v>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>OCTRIDE INJ 100MCG/1ML</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F185" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>5</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>OCTRIDEINJ'|ooMCG/|ML</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>2</v>
-      </c>
-      <c r="E186" t="n">
-        <v>550</v>
-      </c>
-      <c r="F186" t="n">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>5</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>POLYFLUSH SYRINGE 10ML</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>4</v>
-      </c>
-      <c r="E187" t="n">
-        <v>222</v>
-      </c>
-      <c r="F187" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>5</v>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>MBLET TAB 2OMG</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>5</v>
-      </c>
-      <c r="E188" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="F188" t="n">
-        <v>71.75</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>5</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>'TMLSYRTUBERCULTN</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>3</v>
-      </c>
-      <c r="E189" t="n">
-        <v>72</v>
-      </c>
-      <c r="F189" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>5</v>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>OCTRIDEINJ Io0MCG/1ML</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>3</v>
-      </c>
-      <c r="E190" t="n">
-        <v>4950</v>
-      </c>
-      <c r="F190" t="n">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>doc3.pdf</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>5</v>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>REVELOLAM 5O/5TAB</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>2</v>
-      </c>
-      <c r="E191" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="F191" t="n">
-        <v>32.24</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
